--- a/Exchel/Parkside.xlsx
+++ b/Exchel/Parkside.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nektarios\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nektarios\Documents\Nektarios Tsiounis\parkside\Exchel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97FBBD06-C894-410E-819C-29B4B1865CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF2B283-FCC5-4208-BF88-5237089AA2A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{73245B6A-1372-4FDF-A04A-6684546584CB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="130">
   <si>
     <t>Title</t>
   </si>
@@ -365,6 +365,66 @@
   </si>
   <si>
     <t>Ονομαστική ισχύς: 160 W | Αριθμός στροφών χωρίς φορτίο: n 10000–40000 min⁻¹ (Ρυθμιζόμενος) | Διάμετρος σφιγκτήρων: Ø 2,4 mm / Ø 3,2 mm (προεγκατεστημένοι) | Μήκος καλωδίου: 4 m | Χαρακτηριστικά: Ασφάλεια ατράκτου, Φωτισμός LED, Αντιολισθητική λαβή | Περιλαμβάνει: 1 ευέλικτο άξονα (ντίζα), 1 τηλεσκοπική βάση με σφιγκτήρα και γάντζο ανάρτησης, 1 εξάρτημα φρέζας, κασετίνα 42 εξαρτημάτων, μπαταρίες για το LED, βαλιτσάκι μεταφοράς</t>
+  </si>
+  <si>
+    <t>Ντουζιέρα ηλιακή</t>
+  </si>
+  <si>
+    <t>Προέκταση καλωδίου 10m</t>
+  </si>
+  <si>
+    <t>Βυθιζόμενη αντλία αποστράγγισης καθαρού νερού PETPK 400 B2</t>
+  </si>
+  <si>
+    <t>Ψεκαστήρας 5l</t>
+  </si>
+  <si>
+    <t>Ηλεκτρικό χορτοκοπτικό μεσινέζας PERT 550 C6</t>
+  </si>
+  <si>
+    <t>Ηλιακό σετ ποτίσματος</t>
+  </si>
+  <si>
+    <t>Ανταλλακτικές κεφαλές μεσινέζας</t>
+  </si>
+  <si>
+    <t>Κλαδοτεμαχιστής PEMH 2400 B2</t>
+  </si>
+  <si>
+    <t>Επαναφορτιζόμενος ανιχνευτής μετάλλων 4V PAMD 4 A1</t>
+  </si>
+  <si>
+    <t>Μπλούζα</t>
+  </si>
+  <si>
+    <t>Πάτοι παπουτσιών τζελ</t>
+  </si>
+  <si>
+    <t>Κάλτσες εργασίας</t>
+  </si>
+  <si>
+    <t>Φορητό ψυγείο μπαταρίας PKB 20-Li A2 20V</t>
+  </si>
+  <si>
+    <t>Επιτραπέζιο δράπανο PTBM 450 A1</t>
+  </si>
+  <si>
+    <t>Επαναφορτιζόμενος γωνιακός τροχός 20V PWSA 20-Li G4</t>
+  </si>
+  <si>
+    <t>Σετ κατσαβίδι με καρυδάκια και bits</t>
+  </si>
+  <si>
+    <t>Σετ κλειδιά με καρυδάκια και bits</t>
+  </si>
+  <si>
+    <t>Συσκευή λείανσης και διάτρησης PFBS 160 D3</t>
+  </si>
+  <si>
+    <t>second_image</t>
+  </si>
+  <si>
+    <t>Σετ κατσαβίδι καστάνιας με bits διπλής κεφαλής</t>
   </si>
 </sst>
 </file>
@@ -741,7 +801,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66B6ABC7-E05E-478E-A12C-400B5389E091}">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.85546875" style="3" customWidth="1"/>
@@ -749,17 +809,17 @@
     <col min="3" max="3" width="17.85546875" style="4" customWidth="1"/>
     <col min="4" max="4" width="30.42578125" style="3" customWidth="1"/>
     <col min="5" max="5" width="38.140625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="25.7109375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="35" style="4" customWidth="1"/>
     <col min="7" max="7" width="31.42578125" style="4" customWidth="1"/>
     <col min="8" max="8" width="21.85546875" style="4" customWidth="1"/>
     <col min="9" max="9" width="20.7109375" style="4" customWidth="1"/>
     <col min="10" max="10" width="16.28515625" style="1" customWidth="1"/>
     <col min="11" max="11" width="22.7109375" style="4" customWidth="1"/>
     <col min="12" max="13" width="17.85546875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="9.140625" style="1"/>
+    <col min="14" max="14" width="21" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -799,8 +859,11 @@
       <c r="M1" s="4" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>32</v>
       </c>
@@ -816,8 +879,8 @@
       <c r="E2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="4">
-        <v>1</v>
+      <c r="F2" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>10</v>
@@ -832,7 +895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>31</v>
       </c>
@@ -848,8 +911,8 @@
       <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="4">
-        <v>1</v>
+      <c r="F3" s="4" t="s">
+        <v>111</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>20</v>
@@ -864,7 +927,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
@@ -880,8 +943,8 @@
       <c r="E4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="4">
-        <v>1</v>
+      <c r="F4" s="4" t="s">
+        <v>112</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>27</v>
@@ -896,7 +959,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>29</v>
       </c>
@@ -912,8 +975,8 @@
       <c r="E5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="4">
-        <v>1</v>
+      <c r="F5" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>27</v>
@@ -928,7 +991,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>36</v>
       </c>
@@ -944,8 +1007,8 @@
       <c r="E6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="4">
-        <v>1</v>
+      <c r="F6" s="4" t="s">
+        <v>114</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>27</v>
@@ -960,7 +1023,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>42</v>
       </c>
@@ -976,8 +1039,8 @@
       <c r="E7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="4">
-        <v>1</v>
+      <c r="F7" s="4" t="s">
+        <v>115</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>26</v>
@@ -995,7 +1058,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>49</v>
       </c>
@@ -1011,8 +1074,8 @@
       <c r="E8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="4">
-        <v>1</v>
+      <c r="F8" s="4" t="s">
+        <v>116</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>22</v>
@@ -1024,7 +1087,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>54</v>
       </c>
@@ -1040,8 +1103,8 @@
       <c r="E9" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="4">
-        <v>1</v>
+      <c r="F9" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>27</v>
@@ -1056,7 +1119,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>58</v>
       </c>
@@ -1072,8 +1135,8 @@
       <c r="E10" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="4">
-        <v>2</v>
+      <c r="F10" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>62</v>
@@ -1091,7 +1154,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>66</v>
       </c>
@@ -1107,8 +1170,8 @@
       <c r="E11" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="4">
-        <v>3</v>
+      <c r="F11" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>69</v>
@@ -1123,7 +1186,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>73</v>
       </c>
@@ -1139,8 +1202,8 @@
       <c r="E12" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F12" s="4">
-        <v>4</v>
+      <c r="F12" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>69</v>
@@ -1155,7 +1218,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>76</v>
       </c>
@@ -1171,8 +1234,8 @@
       <c r="E13" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F13" s="4">
-        <v>5</v>
+      <c r="F13" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>69</v>
@@ -1187,7 +1250,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>80</v>
       </c>
@@ -1203,8 +1266,8 @@
       <c r="E14" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F14" s="4">
-        <v>6</v>
+      <c r="F14" s="4" t="s">
+        <v>122</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>62</v>
@@ -1225,7 +1288,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>85</v>
       </c>
@@ -1241,8 +1304,8 @@
       <c r="E15" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F15" s="4">
-        <v>7</v>
+      <c r="F15" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>90</v>
@@ -1260,7 +1323,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>92</v>
       </c>
@@ -1276,8 +1339,8 @@
       <c r="E16" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F16" s="4">
-        <v>8</v>
+      <c r="F16" s="4" t="s">
+        <v>124</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>95</v>
@@ -1292,7 +1355,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>96</v>
       </c>
@@ -1308,8 +1371,8 @@
       <c r="E17" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F17" s="4">
-        <v>9</v>
+      <c r="F17" s="4" t="s">
+        <v>125</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>95</v>
@@ -1323,8 +1386,11 @@
       <c r="K17" s="4" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="N17" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>102</v>
       </c>
@@ -1340,8 +1406,8 @@
       <c r="E18" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F18" s="4">
-        <v>10</v>
+      <c r="F18" s="4" t="s">
+        <v>126</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>95</v>
@@ -1353,7 +1419,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>106</v>
       </c>
@@ -1369,8 +1435,8 @@
       <c r="E19" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F19" s="4">
-        <v>11</v>
+      <c r="F19" s="4" t="s">
+        <v>127</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>95</v>
@@ -1380,11 +1446,6 @@
       </c>
       <c r="K19" s="4" t="s">
         <v>107</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F20" s="4">
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Exchel/Parkside.xlsx
+++ b/Exchel/Parkside.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nektarios\Documents\Nektarios Tsiounis\parkside\Exchel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF2B283-FCC5-4208-BF88-5237089AA2A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE22306-5ADD-4FD7-B7A6-92636D99CBDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{73245B6A-1372-4FDF-A04A-6684546584CB}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{73245B6A-1372-4FDF-A04A-6684546584CB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
